--- a/product_selector_out/STM8T series.xlsx
+++ b/product_selector_out/STM8T series.xlsx
@@ -1050,7 +1050,7 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AG13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2082,24 +2082,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="Z12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AA12" s="7" t="inlineStr">
@@ -2132,9 +2132,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -2249,24 +2249,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="Z13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AA13" s="7" t="inlineStr">
@@ -2299,9 +2299,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -2416,24 +2416,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="Z14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AA14" s="7" t="inlineStr">
@@ -2466,9 +2466,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2732,7 +2732,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM8TL53C4</t>
+          <t>STM8TL52F4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM8TL53C4</t>
+          <t>STM8TL52F4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2768,138 +2768,6 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM8TL53G4</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM8TL53G4</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM8TL53F4</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM8TL53F4</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM8TL52F4</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM8TL52F4</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
         <is>
           <t>Table 19. Total current consumption in Run mode (1)</t>
         </is>

--- a/product_selector_out/STM8T series.xlsx
+++ b/product_selector_out/STM8T series.xlsx
@@ -1050,7 +1050,7 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AG13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
         </is>
       </c>
     </row>
@@ -2082,24 +2082,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Z12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="Z12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AA12" s="7" t="inlineStr">
@@ -2132,9 +2132,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -2249,24 +2249,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Z13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="Z13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AA13" s="7" t="inlineStr">
@@ -2299,9 +2299,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -2416,24 +2416,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Z14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="Z14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AA14" s="7" t="inlineStr">
@@ -2466,9 +2466,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2732,7 +2732,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM8TL52F4</t>
+          <t>STM8TL53C4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2754,20 +2754,152 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>STM8TL53C4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM8TL53G4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM8TL53G4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM8TL53F4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM8TL53F4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>STM8TL52F4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM8TL52F4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Table 19. Total current consumption in Run mode (1)</t>
         </is>

--- a/product_selector_out/STM8T series.xlsx
+++ b/product_selector_out/STM8T series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG15"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,8 @@
     <col width="23.46484375" customWidth="1" min="30" max="30"/>
     <col width="11.6328125" customWidth="1" min="31" max="31"/>
     <col width="43.6484375" customWidth="1" min="32" max="32"/>
-    <col width="52" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="52" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -716,6 +717,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -883,6 +889,11 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
         </is>
       </c>
@@ -1053,6 +1064,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1220,6 +1236,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1387,6 +1408,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1551,14 +1577,19 @@
       </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
@@ -1578,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG15"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1614,6 +1645,7 @@
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
     <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1800,6 +1832,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -1965,7 +2002,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG11" s="6" t="inlineStr">
+      <c r="AG11" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -2137,6 +2179,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -2304,6 +2351,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2471,6 +2523,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -2633,7 +2690,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG15" s="6" t="inlineStr">
+      <c r="AG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -2641,8 +2703,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
